--- a/artfynd/A 33043-2022 artfynd.xlsx
+++ b/artfynd/A 33043-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33043-2022 artfynd.xlsx
+++ b/artfynd/A 33043-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106821273</v>
+        <v>119822612</v>
       </c>
       <c r="B2" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spångabrokärret, Sm</t>
+          <t>Pårydskogen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557595.8739996753</v>
+        <v>557641</v>
       </c>
       <c r="R2" t="n">
-        <v>6270593.026596449</v>
+        <v>6270595</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,62 +761,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Cluer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Cluer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106821218</v>
+        <v>106821273</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557606.1714138536</v>
+        <v>557596</v>
       </c>
       <c r="R3" t="n">
-        <v>6270606.938340417</v>
+        <v>6270593</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +849,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106821963</v>
+        <v>106821145</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -950,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557532.5920924206</v>
+        <v>557596</v>
       </c>
       <c r="R4" t="n">
-        <v>6270700.12693105</v>
+        <v>6270593</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,19 +951,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106821264</v>
+        <v>106821184</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,7 +1010,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1067,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557575.773653699</v>
+        <v>557612</v>
       </c>
       <c r="R5" t="n">
-        <v>6270609.828269415</v>
+        <v>6270604</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,19 +1053,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106821184</v>
+        <v>106821218</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1112,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1184,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557611.7276957915</v>
+        <v>557606</v>
       </c>
       <c r="R6" t="n">
-        <v>6270604.260028129</v>
+        <v>6270607</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,19 +1155,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,15 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106822567</v>
+        <v>106821232</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,7 +1214,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1301,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557516.358976536</v>
+        <v>557597</v>
       </c>
       <c r="R7" t="n">
-        <v>6270757.191464392</v>
+        <v>6270612</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,19 +1257,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106821232</v>
+        <v>106821264</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1316,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1418,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557596.7219900429</v>
+        <v>557576</v>
       </c>
       <c r="R8" t="n">
-        <v>6270611.766853637</v>
+        <v>6270609</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,19 +1359,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,15 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106821145</v>
+        <v>106821963</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1418,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1535,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557595.8739996753</v>
+        <v>557533</v>
       </c>
       <c r="R9" t="n">
-        <v>6270593.026596449</v>
+        <v>6270701</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,19 +1461,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,6 +1487,618 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>106822049</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Spångabrokärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557641</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6270611</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>106822069</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Spångabrokärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557652</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6270608</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>106822530</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Spångabrokärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>557524</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6270758</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>106822567</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Spångabrokärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557516</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6270757</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>106822621</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spångabrokärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557557</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6270719</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>106822629</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Spångabrokärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557552</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6270747</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33043-2022 artfynd.xlsx
+++ b/artfynd/A 33043-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822612</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106821273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106821145</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106821184</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106821218</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106821232</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106821264</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106821963</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822049</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822069</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822567</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822621</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,8 +2169,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>